--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487499_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487499_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6347</v>
+        <v>4.7827</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4368</v>
+        <v>4.9056</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1979</v>
+        <v>-0.1229</v>
       </c>
       <c r="G2" t="n">
         <v>2.8931</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1137</v>
+        <v>0.2617</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.3452</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9277</v>
+        <v>0.607</v>
       </c>
       <c r="V2" t="n">
         <v>2.2154</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2872</v>
+        <v>0.3909</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0864</v>
+        <v>0.1777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3736</v>
+        <v>0.2132</v>
       </c>
       <c r="G3" t="n">
         <v>2.8379</v>
@@ -688,13 +688,13 @@
         <v>0.5875</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0587</v>
+        <v>0.045</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7722</v>
+        <v>-0.5082</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7135</v>
+        <v>0.5531</v>
       </c>
       <c r="V3" t="n">
         <v>-2.1003</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2388</v>
+        <v>-0.1816</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1922</v>
+        <v>-0.971</v>
       </c>
       <c r="F4" t="n">
-        <v>1.431</v>
+        <v>0.7895</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7443</v>
@@ -766,13 +766,13 @@
         <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5476</v>
+        <v>-0.3264</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4685</v>
+        <v>0.8269</v>
       </c>
       <c r="V4" t="n">
         <v>1.8249</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>H. SANCHEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.931</v>
+        <v>-0.8799</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0054</v>
+        <v>1.2195</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.9364</v>
+        <v>-2.0994</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3324</v>
+        <v>0.0254</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.837</v>
+        <v>-1.081</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4954</v>
+        <v>1.1064</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5866</v>
+        <v>1.0911</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6566</v>
+        <v>-0.131</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2432</v>
+        <v>1.2221</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7458</v>
+        <v>-1.0656</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4936</v>
+        <v>-0.9499</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2521</v>
+        <v>-0.1157</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.1958</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7834</v>
+        <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>0.148</v>
+        <v>-0.1392</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3546</v>
+        <v>-0.2264</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2067</v>
+        <v>0.0872</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6659</v>
+        <v>-1.5495</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4332</v>
+        <v>0.5507</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7673</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ TAPIA</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3835</v>
+        <v>-1.1251</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2415</v>
+        <v>1.7578</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.142</v>
+        <v>-2.8829</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.4034</v>
+        <v>-2.3324</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9136</v>
+        <v>-0.837</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4898</v>
+        <v>-1.4954</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.5367</v>
+        <v>-0.5866</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8949</v>
+        <v>0.6566</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6418</v>
+        <v>-1.2432</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8667</v>
+        <v>-1.7458</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0187</v>
+        <v>-1.4936</v>
       </c>
       <c r="O6" t="n">
-        <v>0.152</v>
+        <v>-0.2521</v>
       </c>
       <c r="P6" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.1958</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
         <v>0.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2158</v>
+        <v>-0.0462</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2745</v>
+        <v>0.107</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0587</v>
+        <v>-0.1532</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. SANCHEZ EXPOSITO</t>
+          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6427</v>
+        <v>-1.2796</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7508</v>
+        <v>0.8605</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3935</v>
+        <v>-2.1401</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0254</v>
+        <v>-0.2491</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.081</v>
+        <v>-2.6796</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1064</v>
+        <v>2.4305</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0911</v>
+        <v>1.1561</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.131</v>
+        <v>-1.3901</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2221</v>
+        <v>2.5462</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0656</v>
+        <v>-1.4052</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9499</v>
+        <v>-1.2895</v>
       </c>
       <c r="O7" t="n">
         <v>-0.1157</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.3917</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.1751</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.7834</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.1958</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.9792</v>
-      </c>
       <c r="S7" t="n">
-        <v>-0.902</v>
+        <v>-0.3058</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6952</v>
+        <v>-0.0041</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2068</v>
+        <v>-0.3017</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5495</v>
+        <v>-0.3329</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5507</v>
+        <v>0.8837</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1003</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
+          <t>Q. HUANG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8644</v>
+        <v>-2.1098</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5964</v>
+        <v>-0.4691</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4609</v>
+        <v>-1.6407</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2491</v>
+        <v>-0.7101</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6796</v>
+        <v>-0.9626</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4305</v>
+        <v>0.2525</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1561</v>
+        <v>0.9117</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3901</v>
+        <v>0.2602</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5462</v>
+        <v>0.6515</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4052</v>
+        <v>-1.6218</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2895</v>
+        <v>-1.2228</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1157</v>
+        <v>-0.399</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3917</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1751</v>
+        <v>-2.1543</v>
       </c>
       <c r="R8" t="n">
         <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8907</v>
+        <v>-0.0863</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2682</v>
+        <v>0.1653</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.2516</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3329</v>
+        <v>0.0576</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8837</v>
+        <v>0.6083</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2166</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q. HUANG</t>
+          <t>S. RODRÍGUEZ TAPIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2494</v>
+        <v>-2.3428</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5285</v>
+        <v>-2.3078</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7209</v>
+        <v>-0.035</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7101</v>
+        <v>-2.4034</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9626</v>
+        <v>-1.9136</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2525</v>
+        <v>-0.4898</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9117</v>
+        <v>-1.5367</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2602</v>
+        <v>-0.8949</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6515</v>
+        <v>-0.6418</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6218</v>
+        <v>-0.8667</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2228</v>
+        <v>-1.0187</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.399</v>
+        <v>0.152</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3709</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
         <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2259</v>
+        <v>0.2564</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1059</v>
+        <v>0.2082</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3318</v>
+        <v>0.0482</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.8275</v>
+        <v>-7.3985</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.754</v>
+        <v>-5.5923</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0736</v>
+        <v>-1.8062</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3586</v>
@@ -1234,13 +1234,13 @@
         <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7064</v>
+        <v>-0.2773</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4288</v>
+        <v>-0.267</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2776</v>
+        <v>-0.0103</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1267,28 +1267,28 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.7378</v>
+        <v>-10.1437</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.013199999999999</v>
+        <v>-0.4191000000000003</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.724799999999998</v>
+        <v>-9.724500000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0415</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.093400000000001</v>
+        <v>-4.0934</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05200000000000005</v>
+        <v>0.05199999999999982</v>
       </c>
       <c r="J11" t="n">
-        <v>6.297000000000001</v>
+        <v>6.297</v>
       </c>
       <c r="K11" t="n">
-        <v>6.426700000000001</v>
+        <v>6.4267</v>
       </c>
       <c r="L11" t="n">
         <v>-0.1296000000000004</v>
@@ -1300,7 +1300,7 @@
         <v>-10.52</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1817</v>
+        <v>0.1817000000000001</v>
       </c>
       <c r="P11" t="n">
         <v>-5.875299999999999</v>
@@ -1312,10 +1312,10 @@
         <v>8.8131</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3853000000000002</v>
+        <v>0.2087999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.791</v>
+        <v>-1.1968</v>
       </c>
       <c r="U11" t="n">
         <v>1.4056</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4158</v>
+        <v>4.3585</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7285</v>
+        <v>2.5238</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6873</v>
+        <v>1.8347</v>
       </c>
       <c r="G12" t="n">
         <v>2.5954</v>
@@ -1390,13 +1390,13 @@
         <v>2.1543</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0073</v>
+        <v>0.95</v>
       </c>
       <c r="T12" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.1294</v>
       </c>
       <c r="U12" t="n">
-        <v>1.932</v>
+        <v>1.0794</v>
       </c>
       <c r="V12" t="n">
         <v>0.6173</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4368</v>
+        <v>4.2987</v>
       </c>
       <c r="E13" t="n">
-        <v>4.749</v>
+        <v>5.2607</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3123</v>
+        <v>-0.962</v>
       </c>
       <c r="G13" t="n">
         <v>1.6375</v>
@@ -1468,13 +1468,13 @@
         <v>1.5668</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5254</v>
+        <v>-0.6634</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9328</v>
+        <v>-0.4211</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5926</v>
+        <v>-0.2423</v>
       </c>
       <c r="V13" t="n">
         <v>3.7164</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. DOMINGUEZ ITURZA</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4003</v>
+        <v>3.3304</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8767</v>
+        <v>2.4215</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4764</v>
+        <v>0.9089</v>
       </c>
       <c r="G14" t="n">
-        <v>1.374</v>
+        <v>0.8222</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6428</v>
+        <v>2.4036</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2688</v>
+        <v>-1.5814</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3677</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6573</v>
+        <v>1.9224</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2896</v>
+        <v>-1.3241</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9938</v>
+        <v>0.2239</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0145</v>
+        <v>0.4812</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0208</v>
+        <v>-0.2573</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7834</v>
+        <v>1.7626</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>1.7626</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8423</v>
+        <v>-0.2047</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9951</v>
+        <v>-0.277</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1529</v>
+        <v>0.0723</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5993000000000001</v>
+        <v>0.9502</v>
       </c>
       <c r="W14" t="n">
-        <v>0.4931</v>
+        <v>2.1003</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0924</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>M. DOMINGUEZ ITURZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3956</v>
+        <v>2.2122</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8075</v>
+        <v>2.365</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5881</v>
+        <v>-0.1528</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8222</v>
+        <v>1.374</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4036</v>
+        <v>1.6428</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5814</v>
+        <v>-0.2688</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5983000000000001</v>
+        <v>2.3677</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9224</v>
+        <v>2.6573</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3241</v>
+        <v>-0.2896</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2239</v>
+        <v>-0.9938</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4812</v>
+        <v>-1.0145</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2573</v>
+        <v>0.0208</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
         <v>1.7626</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1395</v>
+        <v>0.6542</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.891</v>
+        <v>0.4834</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2484</v>
+        <v>0.1707</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9502</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1003</v>
+        <v>0.4931</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.15</v>
+        <v>-1.0924</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2582</v>
+        <v>2.1679</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3791</v>
+        <v>0.0721</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8791</v>
+        <v>2.0958</v>
       </c>
       <c r="G16" t="n">
         <v>0.6364</v>
@@ -1702,13 +1702,13 @@
         <v>1.9585</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4628</v>
+        <v>0.3724</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3546</v>
+        <v>0.0476</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1082</v>
+        <v>0.3248</v>
       </c>
       <c r="V16" t="n">
         <v>1.159</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4255</v>
+        <v>1.0429</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7431</v>
+        <v>0.3337</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6824</v>
+        <v>0.7091</v>
       </c>
       <c r="G17" t="n">
         <v>0.3337</v>
@@ -1780,13 +1780,13 @@
         <v>0.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.3174</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6822</v>
+        <v>0.2729</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4536</v>
+        <v>0.3825</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7435</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>1.197</v>
+        <v>1.3307</v>
       </c>
       <c r="G18" t="n">
         <v>0.3164</v>
@@ -1858,13 +1858,13 @@
         <v>1.5668</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1003</v>
+        <v>0.0293</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2088</v>
+        <v>-0.4135</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3091</v>
+        <v>0.4427</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5507</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9578</v>
+        <v>-1.5052</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5904</v>
+        <v>-1.4881</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3674</v>
+        <v>-0.0171</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7036</v>
@@ -1936,13 +1936,13 @@
         <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.018</v>
+        <v>0.4346</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0306</v>
+        <v>0.0717</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0126</v>
+        <v>0.3629</v>
       </c>
       <c r="V19" t="n">
         <v>-1.6071</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2878</v>
+        <v>-2.3237</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5614</v>
+        <v>-0.3567</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7264</v>
+        <v>-1.967</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0401</v>
@@ -2014,13 +2014,13 @@
         <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6644</v>
+        <v>-0.7003</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8734</v>
+        <v>-0.6687</v>
       </c>
       <c r="U20" t="n">
-        <v>0.209</v>
+        <v>-0.0316</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7583</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8024</v>
+        <v>-2.5443</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6641</v>
+        <v>-0.4595</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1383</v>
+        <v>-2.0848</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9303</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3802</v>
+        <v>-0.122</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5764</v>
+        <v>-0.3717</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1962</v>
+        <v>0.2497</v>
       </c>
       <c r="V21" t="n">
         <v>-1.492</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>10.7378</v>
+        <v>11.4199</v>
       </c>
       <c r="E22" t="n">
-        <v>9.724499999999999</v>
+        <v>9.724399999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.013100000000001</v>
+        <v>1.6955</v>
       </c>
       <c r="G22" t="n">
         <v>4.041600000000001</v>
@@ -2170,13 +2170,13 @@
         <v>14.6885</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3853</v>
+        <v>1.0675</v>
       </c>
       <c r="T22" t="n">
         <v>-1.4058</v>
       </c>
       <c r="U22" t="n">
-        <v>1.791</v>
+        <v>2.473199999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0.4355000000000004</v>
